--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Documents\Meteo\app meteo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C66DC4-B33D-45CE-8F8F-4DC40F258751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6268915-C83F-478E-B862-2B9E766E9562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2426"/>
+  <dimension ref="A1:F2427"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -48950,6 +48950,26 @@
         <v>62</v>
       </c>
       <c r="F2426" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2427" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B2427" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="C2427" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="D2427" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="E2427" s="3">
+        <v>67</v>
+      </c>
+      <c r="F2427" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6268915-C83F-478E-B862-2B9E766E9562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4796ED-D21C-4218-B417-26559755F45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30570" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48964,7 +48964,7 @@
         <v>29.4</v>
       </c>
       <c r="D2427" s="3">
-        <v>12.3</v>
+        <v>19.5</v>
       </c>
       <c r="E2427" s="3">
         <v>67</v>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4796ED-D21C-4218-B417-26559755F45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4107A315-77B6-4B6B-A58A-3F566F7AF9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30570" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25995" yWindow="1995" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48964,10 +48964,10 @@
         <v>29.4</v>
       </c>
       <c r="D2427" s="3">
-        <v>19.5</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E2427" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2427" s="3">
         <v>0</v>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4107A315-77B6-4B6B-A58A-3F566F7AF9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27531C7-8F48-46ED-A8E7-36114E6ECC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25995" yWindow="1995" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25650" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27531C7-8F48-46ED-A8E7-36114E6ECC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DD211D-AA71-4AFB-B9AD-FC1306D5AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25650" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2427"/>
+  <dimension ref="A1:F2428"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -48970,6 +48970,26 @@
         <v>68</v>
       </c>
       <c r="F2427" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2428" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B2428" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="C2428" s="3">
+        <v>26.2</v>
+      </c>
+      <c r="D2428" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="E2428" s="3">
+        <v>80</v>
+      </c>
+      <c r="F2428" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DD211D-AA71-4AFB-B9AD-FC1306D5AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58A935-6090-474C-B36D-4CC622282EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48978,16 +48978,16 @@
         <v>46294</v>
       </c>
       <c r="B2428" s="3">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="C2428" s="3">
-        <v>26.2</v>
+        <v>29.2</v>
       </c>
       <c r="D2428" s="3">
-        <v>17.2</v>
+        <v>20.6</v>
       </c>
       <c r="E2428" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F2428" s="3">
         <v>0</v>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58A935-6090-474C-B36D-4CC622282EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C5D8E1-EDD5-4AEE-A0C4-8CF8F204D22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2428"/>
+  <dimension ref="A1:F2429"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -48990,6 +48990,26 @@
         <v>70</v>
       </c>
       <c r="F2428" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2429" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B2429" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="C2429" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="D2429" s="3">
+        <v>21</v>
+      </c>
+      <c r="E2429" s="3">
+        <v>70</v>
+      </c>
+      <c r="F2429" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C5D8E1-EDD5-4AEE-A0C4-8CF8F204D22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921F88F6-38B0-485B-B241-1E84DE86CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32325" yWindow="1830" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2429"/>
+  <dimension ref="A1:F2430"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49010,6 +49010,26 @@
         <v>70</v>
       </c>
       <c r="F2429" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2430" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B2430" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="C2430" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="D2430" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="E2430" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2430" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921F88F6-38B0-485B-B241-1E84DE86CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4B51E9-2F08-432C-8D54-2C3BDCC7B3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32325" yWindow="1830" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32670" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2430"/>
+  <dimension ref="A1:F2431"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49030,6 +49030,26 @@
         <v>71</v>
       </c>
       <c r="F2430" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2431" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B2431" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="C2431" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="D2431" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="E2431" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2431" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4B51E9-2F08-432C-8D54-2C3BDCC7B3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A154D911-EB3A-4DEF-A9C1-FE09FA9C4F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32670" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31800" yWindow="3150" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49038,13 +49038,13 @@
         <v>46297</v>
       </c>
       <c r="B2431" s="3">
-        <v>14.5</v>
+        <v>15.2</v>
       </c>
       <c r="C2431" s="3">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="D2431" s="3">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="E2431" s="3">
         <v>71</v>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A154D911-EB3A-4DEF-A9C1-FE09FA9C4F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94D6E00-8745-407E-B3AB-D6A20432FF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31800" yWindow="3150" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2431"/>
+  <dimension ref="A1:F2433"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49038,18 +49038,58 @@
         <v>46297</v>
       </c>
       <c r="B2431" s="3">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="C2431" s="3">
-        <v>28.6</v>
+        <v>29.6</v>
       </c>
       <c r="D2431" s="3">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="E2431" s="3">
         <v>71</v>
       </c>
       <c r="F2431" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2432" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B2432" s="3">
+        <v>14.4</v>
+      </c>
+      <c r="C2432" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="D2432" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="E2432" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2432" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2433" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B2433" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="C2433" s="3">
+        <v>29.3</v>
+      </c>
+      <c r="D2433" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="E2433" s="3">
+        <v>73</v>
+      </c>
+      <c r="F2433" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94D6E00-8745-407E-B3AB-D6A20432FF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D458A3-691D-45F2-BBFB-151873483748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2433"/>
+  <dimension ref="A1:F2434"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49090,6 +49090,26 @@
         <v>73</v>
       </c>
       <c r="F2433" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2434" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B2434" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="C2434" s="3">
+        <v>26.6</v>
+      </c>
+      <c r="D2434" s="3">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E2434" s="3">
+        <v>72</v>
+      </c>
+      <c r="F2434" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D458A3-691D-45F2-BBFB-151873483748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB3E4E3-03EA-409A-AC80-AFA657DE1B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2434"/>
+  <dimension ref="A1:F2435"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49110,6 +49110,26 @@
         <v>72</v>
       </c>
       <c r="F2434" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2435" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B2435" s="3">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C2435" s="3">
+        <v>25.2</v>
+      </c>
+      <c r="D2435" s="3">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E2435" s="3">
+        <v>72</v>
+      </c>
+      <c r="F2435" s="3">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB3E4E3-03EA-409A-AC80-AFA657DE1B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201ECE2-CA06-4301-B208-0D7B8DC8F91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2435"/>
+  <dimension ref="A1:F2436"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49130,7 +49130,27 @@
         <v>72</v>
       </c>
       <c r="F2435" s="3">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2436" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B2436" s="3">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C2436" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="D2436" s="3">
+        <v>20.7</v>
+      </c>
+      <c r="E2436" s="3">
+        <v>70</v>
+      </c>
+      <c r="F2436" s="3">
+        <v>24.64</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201ECE2-CA06-4301-B208-0D7B8DC8F91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ADDC33-F5A6-4E17-87F5-CEBEAB59509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="2475" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2436"/>
+  <dimension ref="A1:F2437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49151,6 +49151,26 @@
       </c>
       <c r="F2436" s="3">
         <v>24.64</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2437" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B2437" s="3">
+        <v>16.2</v>
+      </c>
+      <c r="C2437" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="D2437" s="3">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E2437" s="3">
+        <v>83</v>
+      </c>
+      <c r="F2437" s="3">
+        <v>35.31</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ADDC33-F5A6-4E17-87F5-CEBEAB59509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E6DF9B-EBD0-4CBF-AD05-9AD90DF77967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2475" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2437"/>
+  <dimension ref="A1:F2443"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49171,6 +49171,126 @@
       </c>
       <c r="F2437" s="3">
         <v>35.31</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2438" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B2438" s="3">
+        <v>15.4</v>
+      </c>
+      <c r="C2438" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="D2438" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="E2438" s="3">
+        <v>89</v>
+      </c>
+      <c r="F2438" s="3">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2439" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B2439" s="3">
+        <v>15.3</v>
+      </c>
+      <c r="C2439" s="3">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D2439" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="E2439" s="3">
+        <v>91</v>
+      </c>
+      <c r="F2439" s="3">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2440" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B2440" s="3">
+        <v>13</v>
+      </c>
+      <c r="C2440" s="3">
+        <v>25.8</v>
+      </c>
+      <c r="D2440" s="3">
+        <v>18.3</v>
+      </c>
+      <c r="E2440" s="3">
+        <v>80</v>
+      </c>
+      <c r="F2440" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2441" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B2441">
+        <v>14.2</v>
+      </c>
+      <c r="C2441">
+        <v>25.2</v>
+      </c>
+      <c r="D2441">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E2441">
+        <v>73</v>
+      </c>
+      <c r="F2441">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2442" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B2442">
+        <v>11.7</v>
+      </c>
+      <c r="C2442">
+        <v>23.6</v>
+      </c>
+      <c r="D2442">
+        <v>17.2</v>
+      </c>
+      <c r="E2442">
+        <v>60</v>
+      </c>
+      <c r="F2442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2443" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B2443">
+        <v>10.5</v>
+      </c>
+      <c r="C2443">
+        <v>25.6</v>
+      </c>
+      <c r="D2443">
+        <v>16.7</v>
+      </c>
+      <c r="E2443">
+        <v>62</v>
+      </c>
+      <c r="F2443">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E6DF9B-EBD0-4CBF-AD05-9AD90DF77967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC7180-6637-4F74-84CB-1216D1FCBF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2443"/>
+  <dimension ref="A1:F2444"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49290,6 +49290,26 @@
         <v>62</v>
       </c>
       <c r="F2443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2444" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B2444">
+        <v>9.5</v>
+      </c>
+      <c r="C2444">
+        <v>25.3</v>
+      </c>
+      <c r="D2444">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E2444">
+        <v>72</v>
+      </c>
+      <c r="F2444">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC7180-6637-4F74-84CB-1216D1FCBF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464DC5B0-FD2D-41F3-92FF-7DA9B5251D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2444"/>
+  <dimension ref="A1:F2448"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49310,6 +49310,86 @@
         <v>72</v>
       </c>
       <c r="F2444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2445" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B2445">
+        <v>11.1</v>
+      </c>
+      <c r="C2445">
+        <v>25.4</v>
+      </c>
+      <c r="D2445">
+        <v>17</v>
+      </c>
+      <c r="E2445">
+        <v>73</v>
+      </c>
+      <c r="F2445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2446" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B2446">
+        <v>11.2</v>
+      </c>
+      <c r="C2446">
+        <v>24</v>
+      </c>
+      <c r="D2446">
+        <v>16.7</v>
+      </c>
+      <c r="E2446">
+        <v>77</v>
+      </c>
+      <c r="F2446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2447" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B2447">
+        <v>11.9</v>
+      </c>
+      <c r="C2447">
+        <v>23.9</v>
+      </c>
+      <c r="D2447">
+        <v>17.2</v>
+      </c>
+      <c r="E2447">
+        <v>81</v>
+      </c>
+      <c r="F2447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2448" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B2448">
+        <v>11.7</v>
+      </c>
+      <c r="C2448">
+        <v>24.7</v>
+      </c>
+      <c r="D2448">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E2448">
+        <v>77</v>
+      </c>
+      <c r="F2448">
         <v>0</v>
       </c>
     </row>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464DC5B0-FD2D-41F3-92FF-7DA9B5251D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21CF4E9-C1C0-4CC9-8ABC-98470ED6026B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2448"/>
+  <dimension ref="A1:F2449"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49391,6 +49391,26 @@
       </c>
       <c r="F2448">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2449" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B2449">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="C2449">
+        <v>24.3</v>
+      </c>
+      <c r="D2449">
+        <v>17.3</v>
+      </c>
+      <c r="E2449">
+        <v>76</v>
+      </c>
+      <c r="F2449">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21CF4E9-C1C0-4CC9-8ABC-98470ED6026B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A293F61D-C8A0-4E52-A875-0BF048203462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2449"/>
+  <dimension ref="A1:F2450"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49411,6 +49411,26 @@
       </c>
       <c r="F2449">
         <v>3.3</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2450" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2450">
+        <v>13.8</v>
+      </c>
+      <c r="C2450">
+        <v>20.8</v>
+      </c>
+      <c r="D2450">
+        <v>17.7</v>
+      </c>
+      <c r="E2450">
+        <v>68</v>
+      </c>
+      <c r="F2450">
+        <v>35.31</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A293F61D-C8A0-4E52-A875-0BF048203462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B044993-BA11-42B5-B767-CC19355C0A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -428,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2450"/>
+  <dimension ref="A1:F2451"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49431,6 +49444,26 @@
       </c>
       <c r="F2450">
         <v>35.31</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2451" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2451">
+        <v>11.2</v>
+      </c>
+      <c r="C2451">
+        <v>23.1</v>
+      </c>
+      <c r="D2451">
+        <v>15.8</v>
+      </c>
+      <c r="E2451">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="F2451">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B044993-BA11-42B5-B767-CC19355C0A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CCF009-A651-42BE-BABD-AFB18392DF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2451"/>
+  <dimension ref="A1:F2453"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49464,6 +49464,46 @@
       </c>
       <c r="F2451">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2452" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2452">
+        <v>8.1</v>
+      </c>
+      <c r="C2452">
+        <v>21.8</v>
+      </c>
+      <c r="D2452">
+        <v>14.6</v>
+      </c>
+      <c r="E2452">
+        <v>76</v>
+      </c>
+      <c r="F2452">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2453" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2453">
+        <v>10.4</v>
+      </c>
+      <c r="C2453">
+        <v>19.2</v>
+      </c>
+      <c r="D2453">
+        <v>15.5</v>
+      </c>
+      <c r="E2453">
+        <v>78</v>
+      </c>
+      <c r="F2453">
+        <v>1.78</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robpi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CCF009-A651-42BE-BABD-AFB18392DF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CE4566-AAAB-4B97-A4B6-DB7A1F58A9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2453"/>
+  <dimension ref="A1:F2455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49504,6 +49504,46 @@
       </c>
       <c r="F2453">
         <v>1.78</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2454" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2454">
+        <v>7.4</v>
+      </c>
+      <c r="C2454">
+        <v>18.3</v>
+      </c>
+      <c r="D2454">
+        <v>12.2</v>
+      </c>
+      <c r="E2454">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="F2454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2455" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2455">
+        <v>10.1</v>
+      </c>
+      <c r="C2455">
+        <v>22.6</v>
+      </c>
+      <c r="D2455">
+        <v>15.3</v>
+      </c>
+      <c r="E2455">
+        <v>72.3</v>
+      </c>
+      <c r="F2455">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dati_meteo_esempio.xlsx
+++ b/dati_meteo_esempio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YZ4035\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CE4566-AAAB-4B97-A4B6-DB7A1F58A9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CE6339-F571-48FE-A88F-1332191EA152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="23925" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2455"/>
+  <dimension ref="A1:F2456"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -49543,6 +49543,26 @@
         <v>72.3</v>
       </c>
       <c r="F2455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2456" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2456">
+        <v>7.6</v>
+      </c>
+      <c r="C2456">
+        <v>20.8</v>
+      </c>
+      <c r="D2456">
+        <v>13.2</v>
+      </c>
+      <c r="E2456">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="F2456">
         <v>0</v>
       </c>
     </row>
